--- a/mock-portal/MockData/supplier_001.xlsx
+++ b/mock-portal/MockData/supplier_001.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -449,7 +449,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INV-001</t>
+          <t>INV-2026-0912</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V00123</t>
+          <t>3707</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foxlink Precision</t>
+          <t>華碩電腦股份有限公司</t>
         </is>
       </c>
     </row>
@@ -550,43 +550,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABC-9981</t>
+          <t>05C531-103530</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Connector housing 12P</t>
+          <t>THERMISTOR NTC.10K 3% SMD 0603</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>1.8</v>
       </c>
       <c r="E12" t="n">
-        <v>6250</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ABC-9982</t>
+          <t>04-888-105003</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Connector pin set</t>
+          <t>C/C.1uF.10V.10% X5R SMD 0402</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>200</v>
+        <v>20000</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>0.35</v>
       </c>
       <c r="E13" t="n">
-        <v>600</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6850</v>
+        <v>16000</v>
       </c>
     </row>
   </sheetData>
